--- a/data/trans_bre/P3A_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P3A_R-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-24,32; 4,55</t>
+          <t>-26,96; 5,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,06; 19,65</t>
+          <t>-10,55; 20,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,93; 19,96</t>
+          <t>-13,01; 20,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-28,57; 14,07</t>
+          <t>-29,28; 13,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-44,5; 10,88</t>
+          <t>-46,13; 15,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-20,46; 47,49</t>
+          <t>-18,64; 51,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-28,35; 81,47</t>
+          <t>-32,62; 82,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-36,87; 19,75</t>
+          <t>-35,76; 20,44</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 5,38</t>
+          <t>-7,43; 5,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 7,59</t>
+          <t>-5,57; 7,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 6,8</t>
+          <t>-4,9; 6,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 4,96</t>
+          <t>-3,48; 5,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-16,91; 14,85</t>
+          <t>-17,7; 15,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 25,75</t>
+          <t>-14,76; 25,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-13,41; 21,62</t>
+          <t>-13,38; 21,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 5,98</t>
+          <t>-3,91; 6,29</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 16,1</t>
+          <t>-0,94; 16,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,05; 4,96</t>
+          <t>-13,18; 5,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,31; 3,28</t>
+          <t>-13,17; 3,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 4,67</t>
+          <t>-6,72; 5,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 87,78</t>
+          <t>-3,23; 95,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-40,01; 22,73</t>
+          <t>-40,68; 26,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-40,44; 13,98</t>
+          <t>-41,02; 12,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 5,28</t>
+          <t>-7,18; 5,76</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 4,04</t>
+          <t>-4,84; 4,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 5,82</t>
+          <t>-4,21; 5,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 4,3</t>
+          <t>-4,98; 3,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 3,37</t>
+          <t>-4,16; 3,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-14,66; 12,01</t>
+          <t>-12,89; 12,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-11,83; 19,02</t>
+          <t>-11,82; 17,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-14,77; 13,75</t>
+          <t>-14,32; 13,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 3,99</t>
+          <t>-4,77; 4,01</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P3A_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P3A_R-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-26,96; 5,49</t>
+          <t>-24,51; 6,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,55; 20,67</t>
+          <t>-9,7; 20,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,01; 20,44</t>
+          <t>-11,94; 19,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-29,28; 13,85</t>
+          <t>-27,22; 14,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-46,13; 15,12</t>
+          <t>-43,01; 17,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-18,64; 51,23</t>
+          <t>-17,37; 49,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-32,62; 82,08</t>
+          <t>-30,78; 80,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-35,76; 20,44</t>
+          <t>-36,19; 21,79</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 5,3</t>
+          <t>-7,42; 5,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 7,69</t>
+          <t>-4,48; 7,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 6,66</t>
+          <t>-5,15; 6,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 5,3</t>
+          <t>-3,76; 4,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-17,7; 15,16</t>
+          <t>-17,97; 14,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-14,76; 25,62</t>
+          <t>-12,19; 23,45</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-13,38; 21,22</t>
+          <t>-13,85; 20,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 6,29</t>
+          <t>-4,22; 5,78</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 16,45</t>
+          <t>-1,58; 16,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,18; 5,96</t>
+          <t>-12,69; 5,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,17; 3,06</t>
+          <t>-14,07; 2,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 5,01</t>
+          <t>-7,02; 4,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 95,46</t>
+          <t>-6,85; 95,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-40,68; 26,81</t>
+          <t>-39,94; 24,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-41,02; 12,71</t>
+          <t>-42,47; 11,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 5,76</t>
+          <t>-7,64; 5,08</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 4,03</t>
+          <t>-4,91; 4,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 5,55</t>
+          <t>-4,1; 5,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 3,99</t>
+          <t>-5,32; 3,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 3,41</t>
+          <t>-3,97; 3,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-12,89; 12,07</t>
+          <t>-12,93; 13,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-11,82; 17,6</t>
+          <t>-11,58; 17,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-14,32; 13,0</t>
+          <t>-15,15; 12,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 4,01</t>
+          <t>-4,51; 4,3</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P3A_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P3A_R-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-2,71</t>
+          <t>6,6</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-3,7%</t>
+          <t>8,94%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-24,51; 6,79</t>
+          <t>-24,32; 4,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,7; 20,51</t>
+          <t>-11,06; 19,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,94; 19,99</t>
+          <t>-11,93; 19,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-27,22; 14,97</t>
+          <t>-8,74; 21,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-43,01; 17,5</t>
+          <t>-44,5; 10,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-17,37; 49,5</t>
+          <t>-20,46; 47,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-30,78; 80,36</t>
+          <t>-28,35; 81,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-36,19; 21,79</t>
+          <t>-10,99; 33,06</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,48</t>
+          <t>0,55</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 5,08</t>
+          <t>-6,82; 5,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 7,32</t>
+          <t>-4,73; 7,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 6,49</t>
+          <t>-4,95; 6,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 4,86</t>
+          <t>-3,32; 4,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-17,97; 14,23</t>
+          <t>-16,91; 14,85</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-12,19; 23,45</t>
+          <t>-12,93; 25,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-13,85; 20,28</t>
+          <t>-13,41; 21,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 5,78</t>
+          <t>-3,78; 5,45</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,0</t>
+          <t>-0,86</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-1,11%</t>
+          <t>-0,96%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 16,43</t>
+          <t>-1,66; 16,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,69; 5,19</t>
+          <t>-13,05; 4,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,07; 2,94</t>
+          <t>-13,31; 3,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 4,37</t>
+          <t>-6,94; 4,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 95,91</t>
+          <t>-6,84; 87,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-39,94; 24,21</t>
+          <t>-40,01; 22,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-42,47; 11,85</t>
+          <t>-40,44; 13,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 5,08</t>
+          <t>-7,42; 5,47</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,19</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-0,22%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 4,48</t>
+          <t>-5,66; 4,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 5,45</t>
+          <t>-4,27; 5,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 3,91</t>
+          <t>-5,25; 4,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 3,59</t>
+          <t>-2,59; 3,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 13,32</t>
+          <t>-14,66; 12,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-11,58; 17,26</t>
+          <t>-11,83; 19,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-15,15; 12,08</t>
+          <t>-14,77; 13,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 4,3</t>
+          <t>-2,99; 4,74</t>
         </is>
       </c>
     </row>
